--- a/VO_Manifest.xlsx
+++ b/VO_Manifest.xlsx
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>अपनी जेट स्की चुनिए।</t>
+          <t>अपनी नाव चुनिए।</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>बहुत बढ़िया! आपने सीख लिया। जोड़ते समय पहले 10 बनाइए और बाकी जोड़िए। घटाते समय पहले 10 तक आइए और बाकी घटाइए।</t>
+          <t>बहुत बढ़िया! आपने सीख लिया।</t>
         </is>
       </c>
     </row>
